--- a/ingress-workflow_examples/animal/Rosy/NORT_R2/metadata.xlsx
+++ b/ingress-workflow_examples/animal/Rosy/NORT_R2/metadata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="263">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -203,604 +203,610 @@
     <t xml:space="preserve">Trial_ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Perimeter left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perimeter right</t>
+    <t xml:space="preserve">left_object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right_object</t>
   </si>
   <si>
     <t xml:space="preserve">Perimeter</t>
   </si>
   <si>
+    <t xml:space="preserve">OO670_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">670.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO670_1</t>
   </si>
   <si>
-    <t xml:space="preserve">familiar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">670.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO670_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">novel</t>
   </si>
   <si>
+    <t xml:space="preserve">670.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OO671_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO671_1</t>
   </si>
   <si>
-    <t xml:space="preserve">671.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO671_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">671.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO672_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">672.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO672_1</t>
   </si>
   <si>
-    <t xml:space="preserve">672.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO672_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">672.1</t>
   </si>
   <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OO685_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">685.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO685_1</t>
   </si>
   <si>
-    <t xml:space="preserve">685.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO685_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">685.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO686_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO686_1</t>
   </si>
   <si>
-    <t xml:space="preserve">686.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO686_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">686.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO687_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">687.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO687_1</t>
   </si>
   <si>
-    <t xml:space="preserve">687.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO687_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">687.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO725_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO725_1</t>
   </si>
   <si>
-    <t xml:space="preserve">725.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO725_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">725.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO728_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO728_1</t>
   </si>
   <si>
-    <t xml:space="preserve">728.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO728_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">728.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO731_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">731.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO731_1</t>
   </si>
   <si>
-    <t xml:space="preserve">731.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO731_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">731.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO735_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO735_1</t>
   </si>
   <si>
-    <t xml:space="preserve">735.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO735_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">735.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO736_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO736_1</t>
   </si>
   <si>
-    <t xml:space="preserve">736.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO736_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">736.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO737_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO737_1</t>
   </si>
   <si>
-    <t xml:space="preserve">737.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO737_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">737.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO738_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">738.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO738_1</t>
   </si>
   <si>
-    <t xml:space="preserve">738.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO738_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">738.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO743_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">743.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO743_1</t>
   </si>
   <si>
-    <t xml:space="preserve">743.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO743_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">743.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO745_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">745.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO745_1</t>
   </si>
   <si>
-    <t xml:space="preserve">745.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO745_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">745.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO941_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">941.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO941_1</t>
   </si>
   <si>
-    <t xml:space="preserve">941.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO941_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">941.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO942_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">942.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO942_1</t>
   </si>
   <si>
-    <t xml:space="preserve">942.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO942_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">942.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO943_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">943.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO943_1</t>
   </si>
   <si>
-    <t xml:space="preserve">943.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO943_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">943.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO944_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">944.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO944_1</t>
   </si>
   <si>
-    <t xml:space="preserve">944.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO944_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">944.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO945_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">945.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO945_1</t>
   </si>
   <si>
-    <t xml:space="preserve">945.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO945_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">945.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO953_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">953.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO953_1</t>
   </si>
   <si>
-    <t xml:space="preserve">953.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO953_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">953.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO954_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">954.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO954_1</t>
   </si>
   <si>
-    <t xml:space="preserve">954.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO954_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">954.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO955_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">955.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO955_1</t>
   </si>
   <si>
-    <t xml:space="preserve">955.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO955_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">955.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO956_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">956.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO956_1</t>
   </si>
   <si>
-    <t xml:space="preserve">956.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO956_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">956.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO957_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">957.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO957_1</t>
   </si>
   <si>
-    <t xml:space="preserve">957.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO957_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">957.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OO958_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">958.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO958_1</t>
   </si>
   <si>
-    <t xml:space="preserve">958.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO958_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">958.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP210_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP210_1</t>
   </si>
   <si>
-    <t xml:space="preserve">210.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP210_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">210.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP211_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP211_1</t>
   </si>
   <si>
-    <t xml:space="preserve">211.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP211_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">211.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP212_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP212_1</t>
   </si>
   <si>
-    <t xml:space="preserve">212.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP212_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">212.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP213_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP213_1</t>
   </si>
   <si>
-    <t xml:space="preserve">213.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP213_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">213.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP214_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP214_1</t>
   </si>
   <si>
-    <t xml:space="preserve">214.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP214_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">214.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP215_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP215_1</t>
   </si>
   <si>
-    <t xml:space="preserve">215.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP215_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">215.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP216_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP216_1</t>
   </si>
   <si>
-    <t xml:space="preserve">216.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP216_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">216.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP679_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP679_1</t>
   </si>
   <si>
-    <t xml:space="preserve">679.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP679_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">679.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP680_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">680.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP680_1</t>
   </si>
   <si>
-    <t xml:space="preserve">680.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP680_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">680.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP696_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">696.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP696_1</t>
   </si>
   <si>
-    <t xml:space="preserve">696.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP696_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">696.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP700_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP700_1</t>
   </si>
   <si>
-    <t xml:space="preserve">700.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP700_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">700.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP721_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">721.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP721_1</t>
   </si>
   <si>
-    <t xml:space="preserve">721.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP721_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">721.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OP722_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OP722_1</t>
   </si>
   <si>
-    <t xml:space="preserve">722.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP722_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">722.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ311_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ311_1</t>
   </si>
   <si>
-    <t xml:space="preserve">311.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ311_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">311.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ312_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ312_1</t>
   </si>
   <si>
-    <t xml:space="preserve">312.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ312_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">312.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ313_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ313_1</t>
   </si>
   <si>
-    <t xml:space="preserve">313.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ313_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">313.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ314_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ314_1</t>
   </si>
   <si>
-    <t xml:space="preserve">314.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ314_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">314.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ323_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ323_1</t>
   </si>
   <si>
-    <t xml:space="preserve">323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ323_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">323.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ324_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ324_1</t>
   </si>
   <si>
-    <t xml:space="preserve">324.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ324_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">324.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ325_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ325_1</t>
   </si>
   <si>
-    <t xml:space="preserve">325.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ325_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">325.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ326_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ326_1</t>
   </si>
   <si>
-    <t xml:space="preserve">326.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ326_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">326.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ327_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ327_1</t>
   </si>
   <si>
-    <t xml:space="preserve">327.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ327_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">327.1</t>
   </si>
   <si>
+    <t xml:space="preserve">OQ328_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OQ328_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OQ328_2</t>
   </si>
   <si>
     <t xml:space="preserve">328.1</t>
@@ -810,11 +816,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -837,6 +842,14 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -846,12 +859,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -880,25 +900,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -919,705 +951,705 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1637,30 +1669,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E99"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="11.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" s="7" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="0" t="s">
@@ -1669,12 +1699,12 @@
       <c r="C2" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="0" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B3" s="0" t="s">
@@ -1683,13 +1713,13 @@
       <c r="C3" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>670.1</v>
+      <c r="D3" s="0" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>69</v>
+      <c r="A4" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>65</v>
@@ -1697,13 +1727,13 @@
       <c r="C4" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
+      <c r="D4" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>71</v>
+      <c r="A5" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>68</v>
@@ -1711,13 +1741,13 @@
       <c r="C5" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>72</v>
+      <c r="D5" s="0" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>73</v>
+      <c r="A6" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>64</v>
@@ -1725,13 +1755,13 @@
       <c r="C6" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>74</v>
+      <c r="D6" s="0" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>75</v>
+      <c r="A7" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>64</v>
@@ -1739,13 +1769,16 @@
       <c r="C7" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>76</v>
+      <c r="D7" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>77</v>
+      <c r="A8" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>65</v>
@@ -1753,13 +1786,13 @@
       <c r="C8" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>78</v>
+      <c r="D8" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>79</v>
+      <c r="A9" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>68</v>
@@ -1767,13 +1800,13 @@
       <c r="C9" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>80</v>
+      <c r="D9" s="0" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>81</v>
+      <c r="A10" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>64</v>
@@ -1781,13 +1814,13 @@
       <c r="C10" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>82</v>
+      <c r="D10" s="0" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>83</v>
+      <c r="A11" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>64</v>
@@ -1795,13 +1828,13 @@
       <c r="C11" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>84</v>
+      <c r="D11" s="0" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>85</v>
+      <c r="A12" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>65</v>
@@ -1809,13 +1842,13 @@
       <c r="C12" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>86</v>
+      <c r="D12" s="0" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>87</v>
+      <c r="A13" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>68</v>
@@ -1823,13 +1856,13 @@
       <c r="C13" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>88</v>
+      <c r="D13" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>89</v>
+      <c r="A14" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>64</v>
@@ -1837,13 +1870,13 @@
       <c r="C14" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>90</v>
+      <c r="D14" s="0" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>91</v>
+      <c r="A15" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>64</v>
@@ -1851,13 +1884,13 @@
       <c r="C15" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>92</v>
+      <c r="D15" s="0" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>93</v>
+      <c r="A16" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>65</v>
@@ -1865,13 +1898,13 @@
       <c r="C16" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>94</v>
+      <c r="D16" s="0" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>95</v>
+      <c r="A17" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>68</v>
@@ -1879,13 +1912,13 @@
       <c r="C17" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>96</v>
+      <c r="D17" s="0" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>97</v>
+      <c r="A18" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>64</v>
@@ -1893,13 +1926,13 @@
       <c r="C18" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>98</v>
+      <c r="D18" s="0" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>99</v>
+      <c r="A19" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>64</v>
@@ -1907,13 +1940,13 @@
       <c r="C19" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>100</v>
+      <c r="D19" s="0" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>101</v>
+      <c r="A20" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>65</v>
@@ -1921,13 +1954,13 @@
       <c r="C20" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>102</v>
+      <c r="D20" s="0" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>103</v>
+      <c r="A21" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>68</v>
@@ -1935,13 +1968,13 @@
       <c r="C21" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>104</v>
+      <c r="D21" s="0" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>105</v>
+      <c r="A22" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>64</v>
@@ -1949,13 +1982,13 @@
       <c r="C22" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>106</v>
+      <c r="D22" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>107</v>
+      <c r="A23" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>64</v>
@@ -1963,13 +1996,13 @@
       <c r="C23" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>108</v>
+      <c r="D23" s="0" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>109</v>
+      <c r="A24" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>65</v>
@@ -1977,13 +2010,13 @@
       <c r="C24" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>110</v>
+      <c r="D24" s="0" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>111</v>
+      <c r="A25" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>68</v>
@@ -1991,13 +2024,13 @@
       <c r="C25" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>112</v>
+      <c r="D25" s="0" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>113</v>
+      <c r="A26" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>64</v>
@@ -2005,13 +2038,13 @@
       <c r="C26" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>114</v>
+      <c r="D26" s="0" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>115</v>
+      <c r="A27" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>64</v>
@@ -2019,13 +2052,13 @@
       <c r="C27" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>116</v>
+      <c r="D27" s="0" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>117</v>
+      <c r="A28" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>64</v>
@@ -2033,13 +2066,13 @@
       <c r="C28" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>118</v>
+      <c r="D28" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>119</v>
+      <c r="A29" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>64</v>
@@ -2047,13 +2080,13 @@
       <c r="C29" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>120</v>
+      <c r="D29" s="0" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>121</v>
+      <c r="A30" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>65</v>
@@ -2061,13 +2094,13 @@
       <c r="C30" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>122</v>
+      <c r="D30" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>123</v>
+      <c r="A31" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>68</v>
@@ -2075,13 +2108,13 @@
       <c r="C31" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>124</v>
+      <c r="D31" s="0" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>125</v>
+      <c r="A32" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>65</v>
@@ -2089,13 +2122,13 @@
       <c r="C32" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>126</v>
+      <c r="D32" s="0" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>127</v>
+      <c r="A33" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>68</v>
@@ -2103,13 +2136,13 @@
       <c r="C33" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>128</v>
+      <c r="D33" s="0" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>129</v>
+      <c r="A34" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>64</v>
@@ -2117,13 +2150,13 @@
       <c r="C34" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>130</v>
+      <c r="D34" s="0" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>131</v>
+      <c r="A35" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>64</v>
@@ -2131,13 +2164,13 @@
       <c r="C35" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>132</v>
+      <c r="D35" s="0" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>133</v>
+      <c r="A36" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>65</v>
@@ -2145,13 +2178,13 @@
       <c r="C36" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>134</v>
+      <c r="D36" s="0" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>135</v>
+      <c r="A37" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>68</v>
@@ -2159,13 +2192,13 @@
       <c r="C37" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>136</v>
+      <c r="D37" s="0" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>137</v>
+      <c r="A38" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>64</v>
@@ -2173,13 +2206,13 @@
       <c r="C38" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>138</v>
+      <c r="D38" s="0" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>139</v>
+      <c r="A39" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>64</v>
@@ -2187,13 +2220,13 @@
       <c r="C39" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>140</v>
+      <c r="D39" s="0" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>141</v>
+      <c r="A40" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>65</v>
@@ -2201,13 +2234,13 @@
       <c r="C40" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>142</v>
+      <c r="D40" s="0" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>143</v>
+      <c r="A41" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>68</v>
@@ -2215,13 +2248,13 @@
       <c r="C41" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>144</v>
+      <c r="D41" s="0" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>145</v>
+      <c r="A42" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>65</v>
@@ -2229,13 +2262,13 @@
       <c r="C42" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>146</v>
+      <c r="D42" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>147</v>
+      <c r="A43" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>68</v>
@@ -2243,13 +2276,13 @@
       <c r="C43" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>148</v>
+      <c r="D43" s="0" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>149</v>
+      <c r="A44" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>64</v>
@@ -2257,13 +2290,13 @@
       <c r="C44" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>150</v>
+      <c r="D44" s="0" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>151</v>
+      <c r="A45" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>64</v>
@@ -2271,13 +2304,13 @@
       <c r="C45" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>152</v>
+      <c r="D45" s="0" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>153</v>
+      <c r="A46" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>65</v>
@@ -2285,13 +2318,13 @@
       <c r="C46" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>154</v>
+      <c r="D46" s="0" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>155</v>
+      <c r="A47" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>68</v>
@@ -2299,13 +2332,13 @@
       <c r="C47" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>156</v>
+      <c r="D47" s="0" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>157</v>
+      <c r="A48" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="B48" s="0" t="s">
         <v>65</v>
@@ -2313,13 +2346,13 @@
       <c r="C48" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>158</v>
+      <c r="D48" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>159</v>
+      <c r="A49" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>68</v>
@@ -2327,13 +2360,13 @@
       <c r="C49" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>160</v>
+      <c r="D49" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>161</v>
+      <c r="A50" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>65</v>
@@ -2341,13 +2374,13 @@
       <c r="C50" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>162</v>
+      <c r="D50" s="0" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>163</v>
+      <c r="A51" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>68</v>
@@ -2355,13 +2388,13 @@
       <c r="C51" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>164</v>
+      <c r="D51" s="0" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>165</v>
+      <c r="A52" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>64</v>
@@ -2369,13 +2402,13 @@
       <c r="C52" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>166</v>
+      <c r="D52" s="0" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>167</v>
+      <c r="A53" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>64</v>
@@ -2383,13 +2416,13 @@
       <c r="C53" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>168</v>
+      <c r="D53" s="0" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>169</v>
+      <c r="A54" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>64</v>
@@ -2397,13 +2430,13 @@
       <c r="C54" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>170</v>
+      <c r="D54" s="0" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>171</v>
+      <c r="A55" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>64</v>
@@ -2411,13 +2444,13 @@
       <c r="C55" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>172</v>
+      <c r="D55" s="0" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>173</v>
+      <c r="A56" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>64</v>
@@ -2425,13 +2458,13 @@
       <c r="C56" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>174</v>
+      <c r="D56" s="0" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>175</v>
+      <c r="A57" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>64</v>
@@ -2439,13 +2472,13 @@
       <c r="C57" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>176</v>
+      <c r="D57" s="0" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>177</v>
+      <c r="A58" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>64</v>
@@ -2453,13 +2486,13 @@
       <c r="C58" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>178</v>
+      <c r="D58" s="0" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>179</v>
+      <c r="A59" s="5" t="s">
+        <v>181</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>64</v>
@@ -2467,13 +2500,13 @@
       <c r="C59" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>180</v>
+      <c r="D59" s="0" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>181</v>
+      <c r="A60" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>64</v>
@@ -2481,13 +2514,13 @@
       <c r="C60" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>182</v>
+      <c r="D60" s="0" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>183</v>
+      <c r="A61" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="B61" s="0" t="s">
         <v>64</v>
@@ -2495,13 +2528,13 @@
       <c r="C61" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>184</v>
+      <c r="D61" s="0" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>185</v>
+      <c r="A62" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>64</v>
@@ -2509,13 +2542,13 @@
       <c r="C62" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>186</v>
+      <c r="D62" s="0" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>187</v>
+      <c r="A63" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>64</v>
@@ -2523,13 +2556,13 @@
       <c r="C63" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>188</v>
+      <c r="D63" s="0" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>189</v>
+      <c r="A64" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>64</v>
@@ -2537,13 +2570,13 @@
       <c r="C64" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>190</v>
+      <c r="D64" s="0" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>191</v>
+      <c r="A65" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>64</v>
@@ -2551,13 +2584,13 @@
       <c r="C65" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>192</v>
+      <c r="D65" s="0" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>193</v>
+      <c r="A66" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="B66" s="0" t="s">
         <v>64</v>
@@ -2565,13 +2598,13 @@
       <c r="C66" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>194</v>
+      <c r="D66" s="0" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>195</v>
+      <c r="A67" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>64</v>
@@ -2579,13 +2612,13 @@
       <c r="C67" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>196</v>
+      <c r="D67" s="0" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>197</v>
+      <c r="A68" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>65</v>
@@ -2593,13 +2626,13 @@
       <c r="C68" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>198</v>
+      <c r="D68" s="0" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>199</v>
+      <c r="A69" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>68</v>
@@ -2607,13 +2640,13 @@
       <c r="C69" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>200</v>
+      <c r="D69" s="0" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>201</v>
+      <c r="A70" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>65</v>
@@ -2621,13 +2654,13 @@
       <c r="C70" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>202</v>
+      <c r="D70" s="0" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>203</v>
+      <c r="A71" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>68</v>
@@ -2635,13 +2668,13 @@
       <c r="C71" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>204</v>
+      <c r="D71" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>205</v>
+      <c r="A72" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>65</v>
@@ -2649,13 +2682,13 @@
       <c r="C72" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>206</v>
+      <c r="D72" s="0" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>207</v>
+      <c r="A73" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>68</v>
@@ -2663,13 +2696,13 @@
       <c r="C73" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>208</v>
+      <c r="D73" s="0" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>209</v>
+      <c r="A74" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>65</v>
@@ -2677,13 +2710,13 @@
       <c r="C74" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>210</v>
+      <c r="D74" s="0" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>211</v>
+      <c r="A75" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>68</v>
@@ -2691,13 +2724,13 @@
       <c r="C75" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>212</v>
+      <c r="D75" s="0" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>213</v>
+      <c r="A76" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>65</v>
@@ -2705,13 +2738,13 @@
       <c r="C76" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>214</v>
+      <c r="D76" s="0" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>215</v>
+      <c r="A77" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>68</v>
@@ -2719,13 +2752,13 @@
       <c r="C77" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>216</v>
+      <c r="D77" s="0" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>217</v>
+      <c r="A78" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>65</v>
@@ -2733,13 +2766,13 @@
       <c r="C78" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>218</v>
+      <c r="D78" s="0" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>219</v>
+      <c r="A79" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>68</v>
@@ -2747,13 +2780,13 @@
       <c r="C79" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>220</v>
+      <c r="D79" s="0" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>221</v>
+      <c r="A80" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>64</v>
@@ -2761,13 +2794,13 @@
       <c r="C80" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>222</v>
+      <c r="D80" s="0" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
-        <v>223</v>
+      <c r="A81" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>64</v>
@@ -2775,13 +2808,13 @@
       <c r="C81" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>224</v>
+      <c r="D81" s="0" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
-        <v>225</v>
+      <c r="A82" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>65</v>
@@ -2789,13 +2822,13 @@
       <c r="C82" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>226</v>
+      <c r="D82" s="0" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>227</v>
+      <c r="A83" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>68</v>
@@ -2803,13 +2836,13 @@
       <c r="C83" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>228</v>
+      <c r="D83" s="0" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>229</v>
+      <c r="A84" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>64</v>
@@ -2817,13 +2850,13 @@
       <c r="C84" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>230</v>
+      <c r="D84" s="0" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>231</v>
+      <c r="A85" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>64</v>
@@ -2831,13 +2864,13 @@
       <c r="C85" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>232</v>
+      <c r="D85" s="0" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>233</v>
+      <c r="A86" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>65</v>
@@ -2845,13 +2878,13 @@
       <c r="C86" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>234</v>
+      <c r="D86" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
-        <v>235</v>
+      <c r="A87" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>68</v>
@@ -2859,13 +2892,13 @@
       <c r="C87" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>236</v>
+      <c r="D87" s="0" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
-        <v>237</v>
+      <c r="A88" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>64</v>
@@ -2873,13 +2906,13 @@
       <c r="C88" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>238</v>
+      <c r="D88" s="0" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
-        <v>239</v>
+      <c r="A89" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>64</v>
@@ -2887,13 +2920,13 @@
       <c r="C89" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>240</v>
+      <c r="D89" s="0" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
-        <v>241</v>
+      <c r="A90" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>65</v>
@@ -2901,13 +2934,13 @@
       <c r="C90" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D90" s="4" t="s">
-        <v>242</v>
+      <c r="D90" s="0" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
-        <v>243</v>
+      <c r="A91" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>68</v>
@@ -2915,13 +2948,13 @@
       <c r="C91" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>244</v>
+      <c r="D91" s="0" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
-        <v>245</v>
+      <c r="A92" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>64</v>
@@ -2929,13 +2962,13 @@
       <c r="C92" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>246</v>
+      <c r="D92" s="0" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>247</v>
+      <c r="A93" s="5" t="s">
+        <v>249</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>64</v>
@@ -2943,13 +2976,13 @@
       <c r="C93" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>248</v>
+      <c r="D93" s="0" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
-        <v>249</v>
+      <c r="A94" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>65</v>
@@ -2957,13 +2990,13 @@
       <c r="C94" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>250</v>
+      <c r="D94" s="0" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
-        <v>251</v>
+      <c r="A95" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>68</v>
@@ -2971,13 +3004,13 @@
       <c r="C95" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>252</v>
+      <c r="D95" s="0" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>253</v>
+      <c r="A96" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>64</v>
@@ -2985,13 +3018,13 @@
       <c r="C96" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>254</v>
+      <c r="D96" s="0" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
-        <v>255</v>
+      <c r="A97" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>64</v>
@@ -2999,13 +3032,13 @@
       <c r="C97" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>256</v>
+      <c r="D97" s="0" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
-        <v>257</v>
+      <c r="A98" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>65</v>
@@ -3013,13 +3046,13 @@
       <c r="C98" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D98" s="4" t="s">
-        <v>258</v>
+      <c r="D98" s="0" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
-        <v>259</v>
+      <c r="A99" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>68</v>
@@ -3027,8 +3060,8 @@
       <c r="C99" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>260</v>
+      <c r="D99" s="0" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
